--- a/VerveStacks_BRA_grids_kan/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_BRA_grids_kan/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_BRA_grids_kan\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CA6484F1-0817-4478-B038-B0F7AFF65BB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13E28C18-5701-4096-B00A-B0C03A4298BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -125,7 +125,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8774" uniqueCount="2207">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8764" uniqueCount="2204">
   <si>
     <t>~TFM_INS-AT</t>
   </si>
@@ -6737,15 +6737,6 @@
   </si>
   <si>
     <t>STG</t>
-  </si>
-  <si>
-    <t>Trd_electricity import</t>
-  </si>
-  <si>
-    <t>e_BR15-500,e_BR20-500,e_BR258-500,e_BR303-230,e_BR305-230,e_BR340-500,e_BR37-500,e_BR41-500,e_BR42-500,e_BR63-500,e_BR644-500,e_BR683-500,e_BR689-500,e_BR691-500,e_BR777-500,e_BR803-500,e_BR851-500,e_BR862-500,e_r9328495-500,e_w108224468-500,e_w1090304792-500,e_w287393618-500,e_w32300871-500,e_w32300871-525,e_w32300871-765,e_w525253078-500</t>
-  </si>
-  <si>
-    <t>Trd_electricity export</t>
   </si>
 </sst>
 </file>
@@ -7966,10 +7957,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E62F63A-48C3-47AD-AFB2-B2AA179A2861}">
-  <dimension ref="B2:AJ1072"/>
+  <dimension ref="B2:AF1072"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
-    <row r="2" spans="2:36" x14ac:dyDescent="0.45">
+    <row r="2" spans="2:32" x14ac:dyDescent="0.45">
       <c r="B2" t="s">
         <v>0</v>
       </c>
@@ -7982,11 +7973,8 @@
       <c r="U2" t="s">
         <v>919</v>
       </c>
-      <c r="AH2" t="s">
-        <v>919</v>
-      </c>
-    </row>
-    <row r="3" spans="2:36" x14ac:dyDescent="0.45">
+    </row>
+    <row r="3" spans="2:32" x14ac:dyDescent="0.45">
       <c r="B3" t="s">
         <v>3</v>
       </c>
@@ -8038,17 +8026,8 @@
       <c r="AA3" t="s">
         <v>613</v>
       </c>
-      <c r="AH3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AI3" t="s">
-        <v>614</v>
-      </c>
-      <c r="AJ3" t="s">
-        <v>920</v>
-      </c>
-    </row>
-    <row r="4" spans="2:36" x14ac:dyDescent="0.45">
+    </row>
+    <row r="4" spans="2:32" x14ac:dyDescent="0.45">
       <c r="B4" t="s">
         <v>128</v>
       </c>
@@ -8115,17 +8094,8 @@
       <c r="AF4" t="s">
         <v>2201</v>
       </c>
-      <c r="AH4" t="s">
-        <v>2204</v>
-      </c>
-      <c r="AI4" t="s">
-        <v>2205</v>
-      </c>
-      <c r="AJ4" t="s">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="5" spans="2:36" x14ac:dyDescent="0.45">
+    </row>
+    <row r="5" spans="2:32" x14ac:dyDescent="0.45">
       <c r="B5" t="s">
         <v>129</v>
       </c>
@@ -8189,17 +8159,8 @@
       <c r="AF5" t="s">
         <v>2202</v>
       </c>
-      <c r="AH5" t="s">
-        <v>2206</v>
-      </c>
-      <c r="AI5" t="s">
-        <v>2205</v>
-      </c>
-      <c r="AJ5" t="s">
-        <v>922</v>
-      </c>
-    </row>
-    <row r="6" spans="2:36" x14ac:dyDescent="0.45">
+    </row>
+    <row r="6" spans="2:32" x14ac:dyDescent="0.45">
       <c r="B6" t="s">
         <v>130</v>
       </c>
@@ -8264,7 +8225,7 @@
         <v>2203</v>
       </c>
     </row>
-    <row r="7" spans="2:36" x14ac:dyDescent="0.45">
+    <row r="7" spans="2:32" x14ac:dyDescent="0.45">
       <c r="B7" t="s">
         <v>131</v>
       </c>
@@ -8314,7 +8275,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="8" spans="2:36" x14ac:dyDescent="0.45">
+    <row r="8" spans="2:32" x14ac:dyDescent="0.45">
       <c r="B8" t="s">
         <v>132</v>
       </c>
@@ -8364,7 +8325,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="9" spans="2:36" x14ac:dyDescent="0.45">
+    <row r="9" spans="2:32" x14ac:dyDescent="0.45">
       <c r="B9" t="s">
         <v>133</v>
       </c>
@@ -8414,7 +8375,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="10" spans="2:36" x14ac:dyDescent="0.45">
+    <row r="10" spans="2:32" x14ac:dyDescent="0.45">
       <c r="B10" t="s">
         <v>134</v>
       </c>
@@ -8464,7 +8425,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="11" spans="2:36" x14ac:dyDescent="0.45">
+    <row r="11" spans="2:32" x14ac:dyDescent="0.45">
       <c r="B11" t="s">
         <v>135</v>
       </c>
@@ -8514,7 +8475,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="12" spans="2:36" x14ac:dyDescent="0.45">
+    <row r="12" spans="2:32" x14ac:dyDescent="0.45">
       <c r="B12" t="s">
         <v>136</v>
       </c>
@@ -8564,7 +8525,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="13" spans="2:36" x14ac:dyDescent="0.45">
+    <row r="13" spans="2:32" x14ac:dyDescent="0.45">
       <c r="B13" t="s">
         <v>137</v>
       </c>
@@ -8614,7 +8575,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="14" spans="2:36" x14ac:dyDescent="0.45">
+    <row r="14" spans="2:32" x14ac:dyDescent="0.45">
       <c r="B14" t="s">
         <v>138</v>
       </c>
@@ -8664,7 +8625,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="15" spans="2:36" x14ac:dyDescent="0.45">
+    <row r="15" spans="2:32" x14ac:dyDescent="0.45">
       <c r="B15" t="s">
         <v>139</v>
       </c>
@@ -8714,7 +8675,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="16" spans="2:36" x14ac:dyDescent="0.45">
+    <row r="16" spans="2:32" x14ac:dyDescent="0.45">
       <c r="B16" t="s">
         <v>140</v>
       </c>
